--- a/02_加值成品/生物/生物5-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/生物/生物5-2_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國一(七年級) 生物5-2 無性生殖與有性生殖　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國一(七年級) 生物5-2 無性生殖與有性生殖　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>不需受精的生殖是？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>無性生殖</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>受精</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>遺傳變異</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>出芽</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>單親</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>需雌雄細胞結合的是？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>分裂生殖</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>幾乎相同</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>出芽</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>有性生殖</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>受精</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>無性生殖後代與親代？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>有性生殖</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>遺傳變異</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>通常兩個</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>幾乎相同</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>相似</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>有性生殖後代具？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>出芽</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>幾乎不產生</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>遺傳變異</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>無性生殖</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>變異</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>細菌以什麼生殖？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>通常兩個</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>幾乎相同</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>分裂生殖</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>無性生殖</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>無性</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>酵母菌常以什麼生殖？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>幾乎不產生</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>出芽</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>有性生殖</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>無性生殖</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>無性</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>馬鈴薯繁殖屬？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>營養器官繁殖</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>分裂生殖</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>通常兩個</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>幾乎不產生</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>無性</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>種子繁殖屬哪種生殖？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>幾乎相同</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>受精</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>營養器官繁殖</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>有性生殖</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>受精</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>草莓走莖繁殖屬哪種生殖？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>無性生殖</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>幾乎不產生</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>通常兩個</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>有性生殖</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>無性</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>有性生殖需要幾個親代？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>有性生殖</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>通常兩個</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>出芽</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>遺傳變異</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>雙親</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國一(七年級) 生物5-2 無性生殖與有性生殖　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國一(七年級) 生物5-2 無性生殖與有性生殖　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>無性生殖的優點？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>快速且後代一致</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>無性快速一致但變異少;有性變異多利適應但較慢</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>雌雄細胞結合基因重組</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>後代與親代相同保留優良性狀</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>快速</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>有性生殖的優點？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>增加變異利適應</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>快速保留優良性狀</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>快速且後代一致</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>無性(營養)生殖</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>變異</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>水螅出芽屬哪種生殖？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>無性生殖</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>營養器官繁殖</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>幾乎不產生</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>有性生殖</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>出芽</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>扦插繁殖屬？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>無性(營養)生殖</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>快速保留優良性狀</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>雌雄細胞結合基因重組</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>增加變異利適應</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>無性</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>變異對族群的意義？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>利於適應環境變化</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>增加多樣性提升適應環境能力</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>基因相同缺乏抗性變異</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>馬鈴薯塊莖長出新株、屬無性</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>適應</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>有性生殖需經什麼過程？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>營養器官繁殖</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>受精</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>遺傳變異</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>無性生殖</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>結合</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>無性生殖是否產生變異？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>幾乎不產生</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>分裂生殖</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>遺傳變異</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>受精</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>一致</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>農業用扦插的好處？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>快速保留優良性狀</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>雌雄細胞結合基因重組</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>增加多樣性提升適應環境能力</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>基因相同缺乏抗性變異</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>應用</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>無性生殖後代基因與親代？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>通常兩個</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>幾乎不產生</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>幾乎相同</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>無性生殖</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>一致</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>嫁接繁殖屬哪種生殖？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>無性生殖</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>遺傳變異</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>幾乎相同</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>有性生殖</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>無性</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國一(七年級) 生物5-2 無性生殖與有性生殖　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國一(七年級) 生物5-2 無性生殖與有性生殖　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>比較無性與有性生殖的優缺點？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>無性快速一致但變異少;有性變異多利適應但較慢</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>利於適應環境變化</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>快速保留優良性狀</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>後代與親代相同保留優良性狀</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>對比</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>為何有性生殖產生的變異有利物種生存？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>利於適應環境變化</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>增加多樣性提升適應環境能力</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>快速且後代一致</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>快速保留優良性狀</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>適應</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>農業為何常用無性繁殖保留品種？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>後代與親代相同保留優良性狀</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>有性生殖變異多較能出現適應個體</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>基因相同缺乏抗性變異</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>無性快速一致但變異少;有性變異多利適應但較慢</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>應用</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>環境劇變時何種生殖較有利?為何</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>有性生殖變異多較能出現適應個體</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>基因相同缺乏抗性變異</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>快速且後代一致</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>無性快速一致但變異少;有性變異多利適應但較慢</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>情境</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>無性生殖如何快速增加數量？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>無性快速一致但變異少;有性變異多利適應但較慢</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>增加多樣性提升適應環境能力</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>無性(營養)生殖</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>單親即可分裂或出芽快速繁殖</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>快速</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>有性生殖變異的來源之一？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>雌雄細胞結合基因重組</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>單親即可分裂或出芽快速繁殖</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>利於適應環境變化</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>增加變異利適應</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>來源</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>營養器官繁殖的例子與原理？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>無性快速一致但變異少;有性變異多利適應但較慢</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>利於適應環境變化</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>馬鈴薯塊莖長出新株、屬無性</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>增加變異利適應</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>實例</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>物種若只行無性生殖的風險？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>缺乏變異難應對環境變化</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>利於適應環境變化</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>無性(營養)生殖</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>增加變異利適應</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>風險</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>為何無性繁殖作物易受同種病害全滅？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>無性(營養)生殖</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>有性生殖變異多較能出現適應個體</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>缺乏變異難應對環境變化</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>基因相同缺乏抗性變異</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>風險</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>有性生殖如何增加後代多樣性？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>營養器官繁殖</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>遺傳變異</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>有性生殖</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>雙親基因重組</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>重組</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/生物/生物5-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/生物/生物5-2_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>單親</t>
+          <t>單親繁殖：無性生殖不需要精卵結合受精，只靠一個親代就能產生後代</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>受精</t>
+          <t>兩性結合：有性生殖必須經過雌雄兩種生殖細胞結合受精，才能產生後代</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>相似</t>
+          <t>幾乎相同：無性生殖的後代來自單一親代，遺傳物質與親代幾乎一模一樣</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>變異</t>
+          <t>產生變異：有性生殖由雌雄基因重新組合，讓後代出現和親代不完全相同的變異</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>無性</t>
+          <t>分裂繁殖：細菌是靠自己一分為二的分裂生殖方式來繁衍後代</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>無性</t>
+          <t>出芽生殖：酵母菌常會在身體上長出小芽，芽脫離後長成新個體，稱為出芽生殖</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>無性</t>
+          <t>營養繁殖：馬鈴薯用地下塊莖長出新芽繁殖，屬於利用營養器官的無性生殖</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>受精</t>
+          <t>有性繁殖：種子是植物經過受精作用後形成的，所以種子繁殖屬於有性生殖</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>無性</t>
+          <t>無性：草莓靠走莖長出新植株，不需要經過精卵結合，屬於無性生殖</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>雙親</t>
+          <t>雙親：有性生殖通常需要兩個親代（父方與母方）分別提供精細胞和卵細胞結合，才能產生後代</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>快速</t>
+          <t>快速一致：無性生殖不用尋找配偶交配，繁殖速度快，後代性狀也和親代一致</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>變異</t>
+          <t>增加變異：有性生殖能讓後代出現不同的基因組合，變異有助於適應環境變化</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>出芽</t>
+          <t>出芽方式：水螅靠身體長出芽體再脫離獨立生長，這是一種無性生殖</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>無性</t>
+          <t>營養繁殖：扦插是剪取植物枝條插入土中長出新株，屬於利用營養器官的無性生殖</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>適應</t>
+          <t>適應優勢：族群中個體性狀有差異，遇到環境變化時比較有機會找到能存活下來的個體</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>結合</t>
+          <t>受精過程：有性生殖一定要經過雌雄生殖細胞結合的受精過程才能產生後代</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>一致</t>
+          <t>幾乎不變：無性生殖只來自單一親代複製，後代性狀幾乎不會產生變異</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>應用</t>
+          <t>保留優點：用扦插繁殖能快速大量複製出和原本植株性狀相同的優良品種</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>一致</t>
+          <t>一致：無性生殖不經過基因重組，後代的基因幾乎和親代完全相同，等於是親代的複製品</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>無性</t>
+          <t>無性：嫁接是把植物的一部分接到另一株植物上使其繼續生長，不涉及精卵結合，屬於無性生殖</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>對比</t>
+          <t>各有優劣：無性生殖繁殖快、後代性狀一致但缺乏變異，有性生殖繁殖較慢但變異多有利適應</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>適應</t>
+          <t>提升適應：變異讓族群性狀更多樣，環境改變時比較容易有個體能存活下來延續物種</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>應用</t>
+          <t>保留品種：無性繁殖的後代性狀和親代一致，能穩定保留住原本優良的品種特性</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>情境</t>
+          <t>應變優勢：有性生殖產生的後代變異較多，環境劇變時比較容易出現能適應新環境的個體</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>快速</t>
+          <t>快速增殖：無性生殖不需尋找配偶，單一親代就能靠分裂或出芽迅速增加族群數量</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>來源</t>
+          <t>基因重組：雌雄生殖細胞結合時，雙方基因會重新組合，這是變異產生的來源之一</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>實例</t>
+          <t>實例說明：馬鈴薯利用地下塊莖這種營養器官長出新植株，屬於無性生殖的一種方式</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>風險</t>
+          <t>缺乏變異：只行無性生殖的後代性狀太一致，環境一旦劇烈變化，整個族群可能難以應對而滅絕</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>風險</t>
+          <t>風險：無性繁殖產生的個體基因幾乎完全相同，一旦出現某種病害，因為缺乏基因變異、抗病能力也相同，整批作物可能同時遭殃、全部滅絕</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>重組</t>
+          <t>重組：有性生殖時父母雙方的基因會重新組合，產生的後代基因組合和親代不完全相同，因此能增加後代的多樣性，有助於適應環境變化</t>
         </is>
       </c>
     </row>
